--- a/Documents/ODMS User Matrix.xlsx
+++ b/Documents/ODMS User Matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/richard_almojuela_onetechfilinvest_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CB9CA53-8F0D-4EB1-9B65-201B1C390CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{9CB9CA53-8F0D-4EB1-9B65-201B1C390CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A87D7059-E3B8-4704-8120-D6609D31D5D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7E38F0A5-7DC1-4E86-9AE1-56B89A7A01E9}"/>
   </bookViews>
@@ -40,32 +40,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t>Role</t>
   </si>
   <si>
-    <t>Project Register</t>
-  </si>
-  <si>
-    <t>Executive Dashboard</t>
-  </si>
-  <si>
-    <t>Status Report</t>
-  </si>
-  <si>
-    <t>PM Dashboard</t>
-  </si>
-  <si>
     <t>Approval Page</t>
   </si>
   <si>
-    <t>Admin Page</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -78,33 +60,15 @@
     <t>Edit, View</t>
   </si>
   <si>
-    <t>View (Projects)</t>
-  </si>
-  <si>
     <t>Executive Leadership</t>
   </si>
   <si>
-    <t>View (All)</t>
-  </si>
-  <si>
     <t>Delivery/Portfolio Lead</t>
   </si>
   <si>
-    <t>Approve, Return</t>
-  </si>
-  <si>
-    <t>Tower level</t>
-  </si>
-  <si>
     <t>PMO Admin</t>
   </si>
   <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Add, Edit,View, Delete</t>
-  </si>
-  <si>
     <t>Budget Metrics</t>
   </si>
   <si>
@@ -289,6 +253,15 @@
   </si>
   <si>
     <t>EV ÷ PV</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Project Status Report</t>
+  </si>
+  <si>
+    <t>Approve</t>
   </si>
 </sst>
 </file>
@@ -724,125 +697,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB3BA38-E296-45DD-9E11-330DCBD1C66D}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.36328125" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -853,181 +775,181 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC225F8-0948-4AD9-B4EF-C64CE60EC1A4}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23.45">
+    <row r="1" spans="1:4" ht="23.5">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.5">
       <c r="A3" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.95">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="58">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="29.1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29">
       <c r="A6" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.5">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29">
+      <c r="A8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="29.1">
-      <c r="A8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="43.5">
       <c r="A9" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="57.95">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="58">
       <c r="A10" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="29.1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="29">
       <c r="A11" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="43.5">
       <c r="A12" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="29">
+      <c r="A13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="29.1">
-      <c r="A13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1040,110 +962,116 @@
       <c r="B15" s="4"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="23.45">
+    <row r="16" spans="1:4" ht="23.5">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="43.5">
       <c r="A19" s="5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43.5">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="43.5">
       <c r="A21" s="5" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="43.5">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="57.95">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="58">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="43.5">
       <c r="A24" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{cdb710b6-7041-4093-8e6f-80ac01d6c65a}" enabled="0" method="" siteId="{cdb710b6-7041-4093-8e6f-80ac01d6c65a}" removed="1"/>
+</clbl:labelList>
 </file>